--- a/data/derived_data/2_RarefyData/Dataset_1/ps_rare_16S_sample_data_NF_D1.xlsx
+++ b/data/derived_data/2_RarefyData/Dataset_1/ps_rare_16S_sample_data_NF_D1.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="208">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -320,9 +320,18 @@
     <t xml:space="preserve">MS_090</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_092</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_093</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_095</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_097</t>
   </si>
   <si>
@@ -410,18 +419,21 @@
     <t xml:space="preserve">MS_144</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G1_Adults_Fruits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DaughterFly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daughter</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_146</t>
   </si>
   <si>
-    <t xml:space="preserve">G1_Adults_Fruits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DaughterFly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daughter</t>
-  </si>
-  <si>
     <t xml:space="preserve">MS_153</t>
   </si>
   <si>
@@ -437,13 +449,31 @@
     <t xml:space="preserve">MS_158</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_163</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_164</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_165</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_166</t>
   </si>
   <si>
     <t xml:space="preserve">MS_168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_170</t>
   </si>
   <si>
     <t xml:space="preserve">MS_171</t>
@@ -3503,13 +3533,13 @@
         <v>45</v>
       </c>
       <c r="K44" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="L44" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="M44" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="N44" t="s">
         <v>27</v>
@@ -3535,7 +3565,7 @@
         <v>103</v>
       </c>
       <c r="B45" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C45" t="s">
         <v>21</v>
@@ -3553,22 +3583,22 @@
         <v>25</v>
       </c>
       <c r="H45" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I45" t="s">
         <v>36</v>
       </c>
       <c r="J45" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K45" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L45" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="M45" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="N45" t="s">
         <v>27</v>
@@ -3612,22 +3642,22 @@
         <v>25</v>
       </c>
       <c r="H46" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I46" t="s">
         <v>36</v>
       </c>
       <c r="J46" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K46" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="L46" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="M46" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="N46" t="s">
         <v>27</v>
@@ -3653,7 +3683,7 @@
         <v>105</v>
       </c>
       <c r="B47" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C47" t="s">
         <v>21</v>
@@ -3677,16 +3707,16 @@
         <v>36</v>
       </c>
       <c r="J47" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="K47" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="L47" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="M47" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="N47" t="s">
         <v>27</v>
@@ -3736,16 +3766,16 @@
         <v>36</v>
       </c>
       <c r="J48" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="K48" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="L48" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="M48" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N48" t="s">
         <v>27</v>
@@ -3771,7 +3801,7 @@
         <v>107</v>
       </c>
       <c r="B49" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C49" t="s">
         <v>21</v>
@@ -3795,16 +3825,16 @@
         <v>36</v>
       </c>
       <c r="J49" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="K49" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="L49" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="M49" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="N49" t="s">
         <v>27</v>
@@ -3830,55 +3860,55 @@
         <v>108</v>
       </c>
       <c r="B50" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C50" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D50" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E50" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F50" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="G50" t="s">
         <v>25</v>
       </c>
       <c r="H50" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I50" t="s">
         <v>36</v>
       </c>
       <c r="J50" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="K50" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="L50" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="M50" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="N50" t="s">
         <v>27</v>
       </c>
       <c r="O50" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="P50" t="s">
         <v>28</v>
       </c>
       <c r="Q50" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="R50" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="S50" t="s">
         <v>108</v>
@@ -3886,125 +3916,125 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B51" t="s">
         <v>21</v>
       </c>
       <c r="C51" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D51" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E51" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F51" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="G51" t="s">
         <v>25</v>
       </c>
       <c r="H51" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I51" t="s">
         <v>36</v>
       </c>
       <c r="J51" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="K51" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="L51" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="M51" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="N51" t="s">
         <v>27</v>
       </c>
       <c r="O51" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="P51" t="s">
         <v>28</v>
       </c>
       <c r="Q51" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="R51" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="S51" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B52" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C52" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D52" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E52" t="s">
         <v>23</v>
       </c>
       <c r="F52" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="G52" t="s">
         <v>25</v>
       </c>
       <c r="H52" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I52" t="s">
         <v>36</v>
       </c>
       <c r="J52" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K52" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L52" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="M52" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="N52" t="s">
         <v>27</v>
       </c>
       <c r="O52" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="P52" t="s">
         <v>28</v>
       </c>
       <c r="Q52" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="R52" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="S52" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B53" t="s">
         <v>21</v>
@@ -4013,13 +4043,13 @@
         <v>20</v>
       </c>
       <c r="D53" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E53" t="s">
         <v>51</v>
       </c>
       <c r="F53" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G53" t="s">
         <v>25</v>
@@ -4031,34 +4061,34 @@
         <v>36</v>
       </c>
       <c r="J53" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="K53" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="L53" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="M53" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N53" t="s">
         <v>27</v>
       </c>
       <c r="O53" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="P53" t="s">
         <v>28</v>
       </c>
       <c r="Q53" t="s">
+        <v>114</v>
+      </c>
+      <c r="R53" t="s">
+        <v>27</v>
+      </c>
+      <c r="S53" t="s">
         <v>111</v>
-      </c>
-      <c r="R53" t="s">
-        <v>27</v>
-      </c>
-      <c r="S53" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="54">
@@ -4072,13 +4102,13 @@
         <v>20</v>
       </c>
       <c r="D54" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E54" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="F54" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G54" t="s">
         <v>25</v>
@@ -4090,28 +4120,28 @@
         <v>36</v>
       </c>
       <c r="J54" t="s">
+        <v>58</v>
+      </c>
+      <c r="K54" t="s">
+        <v>59</v>
+      </c>
+      <c r="L54" t="s">
+        <v>60</v>
+      </c>
+      <c r="M54" t="s">
+        <v>61</v>
+      </c>
+      <c r="N54" t="s">
+        <v>27</v>
+      </c>
+      <c r="O54" t="s">
         <v>37</v>
       </c>
-      <c r="K54" t="s">
-        <v>38</v>
-      </c>
-      <c r="L54" t="s">
-        <v>42</v>
-      </c>
-      <c r="M54" t="s">
-        <v>43</v>
-      </c>
-      <c r="N54" t="s">
-        <v>27</v>
-      </c>
-      <c r="O54" t="s">
-        <v>45</v>
-      </c>
       <c r="P54" t="s">
         <v>28</v>
       </c>
       <c r="Q54" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="R54" t="s">
         <v>27</v>
@@ -4131,13 +4161,13 @@
         <v>20</v>
       </c>
       <c r="D55" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E55" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="F55" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G55" t="s">
         <v>25</v>
@@ -4155,10 +4185,10 @@
         <v>38</v>
       </c>
       <c r="L55" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="M55" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="N55" t="s">
         <v>27</v>
@@ -4170,7 +4200,7 @@
         <v>28</v>
       </c>
       <c r="Q55" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="R55" t="s">
         <v>27</v>
@@ -4190,13 +4220,13 @@
         <v>20</v>
       </c>
       <c r="D56" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E56" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="F56" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G56" t="s">
         <v>25</v>
@@ -4208,28 +4238,28 @@
         <v>36</v>
       </c>
       <c r="J56" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="K56" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="L56" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="M56" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N56" t="s">
         <v>27</v>
       </c>
       <c r="O56" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="P56" t="s">
         <v>28</v>
       </c>
       <c r="Q56" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="R56" t="s">
         <v>27</v>
@@ -4249,13 +4279,13 @@
         <v>20</v>
       </c>
       <c r="D57" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E57" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="F57" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G57" t="s">
         <v>25</v>
@@ -4267,28 +4297,28 @@
         <v>36</v>
       </c>
       <c r="J57" t="s">
+        <v>37</v>
+      </c>
+      <c r="K57" t="s">
+        <v>38</v>
+      </c>
+      <c r="L57" t="s">
+        <v>42</v>
+      </c>
+      <c r="M57" t="s">
+        <v>43</v>
+      </c>
+      <c r="N57" t="s">
+        <v>27</v>
+      </c>
+      <c r="O57" t="s">
         <v>45</v>
       </c>
-      <c r="K57" t="s">
-        <v>52</v>
-      </c>
-      <c r="L57" t="s">
-        <v>53</v>
-      </c>
-      <c r="M57" t="s">
-        <v>54</v>
-      </c>
-      <c r="N57" t="s">
-        <v>27</v>
-      </c>
-      <c r="O57" t="s">
-        <v>58</v>
-      </c>
       <c r="P57" t="s">
         <v>28</v>
       </c>
       <c r="Q57" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="R57" t="s">
         <v>27</v>
@@ -4308,13 +4338,13 @@
         <v>20</v>
       </c>
       <c r="D58" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E58" t="s">
         <v>68</v>
       </c>
       <c r="F58" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G58" t="s">
         <v>25</v>
@@ -4326,28 +4356,28 @@
         <v>36</v>
       </c>
       <c r="J58" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="K58" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="L58" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="M58" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="N58" t="s">
         <v>27</v>
       </c>
       <c r="O58" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="P58" t="s">
         <v>28</v>
       </c>
       <c r="Q58" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="R58" t="s">
         <v>27</v>
@@ -4367,13 +4397,13 @@
         <v>20</v>
       </c>
       <c r="D59" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E59" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="F59" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G59" t="s">
         <v>25</v>
@@ -4388,13 +4418,13 @@
         <v>45</v>
       </c>
       <c r="K59" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="L59" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="M59" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="N59" t="s">
         <v>27</v>
@@ -4406,7 +4436,7 @@
         <v>28</v>
       </c>
       <c r="Q59" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="R59" t="s">
         <v>27</v>
@@ -4426,34 +4456,34 @@
         <v>20</v>
       </c>
       <c r="D60" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E60" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F60" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G60" t="s">
         <v>25</v>
       </c>
       <c r="H60" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I60" t="s">
         <v>36</v>
       </c>
       <c r="J60" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="K60" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="L60" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="M60" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="N60" t="s">
         <v>27</v>
@@ -4465,7 +4495,7 @@
         <v>28</v>
       </c>
       <c r="Q60" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="R60" t="s">
         <v>27</v>
@@ -4485,46 +4515,46 @@
         <v>20</v>
       </c>
       <c r="D61" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E61" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F61" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G61" t="s">
         <v>25</v>
       </c>
       <c r="H61" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I61" t="s">
         <v>36</v>
       </c>
       <c r="J61" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="K61" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="L61" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="M61" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="N61" t="s">
         <v>27</v>
       </c>
       <c r="O61" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="P61" t="s">
         <v>28</v>
       </c>
       <c r="Q61" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="R61" t="s">
         <v>27</v>
@@ -4544,46 +4574,46 @@
         <v>20</v>
       </c>
       <c r="D62" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E62" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="F62" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G62" t="s">
         <v>25</v>
       </c>
       <c r="H62" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I62" t="s">
         <v>36</v>
       </c>
       <c r="J62" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K62" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="L62" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="M62" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="N62" t="s">
         <v>27</v>
       </c>
       <c r="O62" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="P62" t="s">
         <v>28</v>
       </c>
       <c r="Q62" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="R62" t="s">
         <v>27</v>
@@ -4603,13 +4633,13 @@
         <v>20</v>
       </c>
       <c r="D63" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E63" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F63" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G63" t="s">
         <v>25</v>
@@ -4621,28 +4651,28 @@
         <v>36</v>
       </c>
       <c r="J63" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="K63" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="L63" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="M63" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N63" t="s">
         <v>27</v>
       </c>
       <c r="O63" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="P63" t="s">
         <v>28</v>
       </c>
       <c r="Q63" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="R63" t="s">
         <v>27</v>
@@ -4662,13 +4692,13 @@
         <v>20</v>
       </c>
       <c r="D64" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E64" t="s">
         <v>51</v>
       </c>
       <c r="F64" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G64" t="s">
         <v>25</v>
@@ -4680,16 +4710,16 @@
         <v>36</v>
       </c>
       <c r="J64" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="K64" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="L64" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="M64" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N64" t="s">
         <v>27</v>
@@ -4701,7 +4731,7 @@
         <v>28</v>
       </c>
       <c r="Q64" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="R64" t="s">
         <v>27</v>
@@ -4721,13 +4751,13 @@
         <v>20</v>
       </c>
       <c r="D65" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E65" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="F65" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G65" t="s">
         <v>25</v>
@@ -4745,10 +4775,10 @@
         <v>38</v>
       </c>
       <c r="L65" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="M65" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="N65" t="s">
         <v>27</v>
@@ -4760,7 +4790,7 @@
         <v>28</v>
       </c>
       <c r="Q65" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="R65" t="s">
         <v>27</v>
@@ -4780,13 +4810,13 @@
         <v>20</v>
       </c>
       <c r="D66" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E66" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="F66" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G66" t="s">
         <v>25</v>
@@ -4804,22 +4834,22 @@
         <v>38</v>
       </c>
       <c r="L66" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="M66" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="N66" t="s">
         <v>27</v>
       </c>
       <c r="O66" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="P66" t="s">
         <v>28</v>
       </c>
       <c r="Q66" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="R66" t="s">
         <v>27</v>
@@ -4839,13 +4869,13 @@
         <v>20</v>
       </c>
       <c r="D67" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E67" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="F67" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G67" t="s">
         <v>25</v>
@@ -4857,28 +4887,28 @@
         <v>36</v>
       </c>
       <c r="J67" t="s">
+        <v>37</v>
+      </c>
+      <c r="K67" t="s">
+        <v>38</v>
+      </c>
+      <c r="L67" t="s">
+        <v>42</v>
+      </c>
+      <c r="M67" t="s">
+        <v>43</v>
+      </c>
+      <c r="N67" t="s">
+        <v>27</v>
+      </c>
+      <c r="O67" t="s">
         <v>45</v>
       </c>
-      <c r="K67" t="s">
-        <v>46</v>
-      </c>
-      <c r="L67" t="s">
-        <v>47</v>
-      </c>
-      <c r="M67" t="s">
-        <v>48</v>
-      </c>
-      <c r="N67" t="s">
-        <v>27</v>
-      </c>
-      <c r="O67" t="s">
-        <v>58</v>
-      </c>
       <c r="P67" t="s">
         <v>28</v>
       </c>
       <c r="Q67" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="R67" t="s">
         <v>27</v>
@@ -4898,13 +4928,13 @@
         <v>20</v>
       </c>
       <c r="D68" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E68" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F68" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G68" t="s">
         <v>25</v>
@@ -4916,28 +4946,28 @@
         <v>36</v>
       </c>
       <c r="J68" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="K68" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="L68" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="M68" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="N68" t="s">
         <v>27</v>
       </c>
       <c r="O68" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="P68" t="s">
         <v>28</v>
       </c>
       <c r="Q68" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="R68" t="s">
         <v>27</v>
@@ -4957,13 +4987,13 @@
         <v>20</v>
       </c>
       <c r="D69" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E69" t="s">
         <v>68</v>
       </c>
       <c r="F69" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G69" t="s">
         <v>25</v>
@@ -4975,16 +5005,16 @@
         <v>36</v>
       </c>
       <c r="J69" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="K69" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="L69" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="M69" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="N69" t="s">
         <v>27</v>
@@ -4996,7 +5026,7 @@
         <v>28</v>
       </c>
       <c r="Q69" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="R69" t="s">
         <v>27</v>
@@ -5016,13 +5046,13 @@
         <v>20</v>
       </c>
       <c r="D70" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E70" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F70" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G70" t="s">
         <v>25</v>
@@ -5037,25 +5067,25 @@
         <v>45</v>
       </c>
       <c r="K70" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="L70" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="M70" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="N70" t="s">
         <v>27</v>
       </c>
       <c r="O70" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="P70" t="s">
         <v>28</v>
       </c>
       <c r="Q70" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="R70" t="s">
         <v>27</v>
@@ -5075,34 +5105,34 @@
         <v>20</v>
       </c>
       <c r="D71" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="E71" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="F71" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="G71" t="s">
         <v>25</v>
       </c>
       <c r="H71" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I71" t="s">
         <v>36</v>
       </c>
       <c r="J71" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="K71" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="L71" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="M71" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="N71" t="s">
         <v>27</v>
@@ -5114,7 +5144,7 @@
         <v>28</v>
       </c>
       <c r="Q71" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="R71" t="s">
         <v>27</v>
@@ -5125,7 +5155,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B72" t="s">
         <v>21</v>
@@ -5134,34 +5164,34 @@
         <v>20</v>
       </c>
       <c r="D72" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="E72" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="F72" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="G72" t="s">
         <v>25</v>
       </c>
       <c r="H72" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I72" t="s">
         <v>36</v>
       </c>
       <c r="J72" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K72" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L72" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="M72" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="N72" t="s">
         <v>27</v>
@@ -5173,18 +5203,18 @@
         <v>28</v>
       </c>
       <c r="Q72" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="R72" t="s">
         <v>27</v>
       </c>
       <c r="S72" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B73" t="s">
         <v>21</v>
@@ -5193,19 +5223,19 @@
         <v>20</v>
       </c>
       <c r="D73" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="E73" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="F73" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="G73" t="s">
         <v>25</v>
       </c>
       <c r="H73" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I73" t="s">
         <v>36</v>
@@ -5214,36 +5244,36 @@
         <v>45</v>
       </c>
       <c r="K73" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="L73" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="M73" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="N73" t="s">
         <v>27</v>
       </c>
       <c r="O73" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="P73" t="s">
         <v>28</v>
       </c>
       <c r="Q73" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="R73" t="s">
         <v>27</v>
       </c>
       <c r="S73" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B74" t="s">
         <v>21</v>
@@ -5252,13 +5282,13 @@
         <v>20</v>
       </c>
       <c r="D74" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E74" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F74" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G74" t="s">
         <v>25</v>
@@ -5270,34 +5300,34 @@
         <v>36</v>
       </c>
       <c r="J74" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="K74" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="L74" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="M74" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="N74" t="s">
         <v>27</v>
       </c>
       <c r="O74" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="P74" t="s">
         <v>28</v>
       </c>
       <c r="Q74" t="s">
+        <v>138</v>
+      </c>
+      <c r="R74" t="s">
+        <v>27</v>
+      </c>
+      <c r="S74" t="s">
         <v>135</v>
-      </c>
-      <c r="R74" t="s">
-        <v>27</v>
-      </c>
-      <c r="S74" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="75">
@@ -5311,13 +5341,13 @@
         <v>20</v>
       </c>
       <c r="D75" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E75" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="F75" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G75" t="s">
         <v>25</v>
@@ -5329,28 +5359,28 @@
         <v>36</v>
       </c>
       <c r="J75" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="K75" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="L75" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="M75" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="N75" t="s">
         <v>27</v>
       </c>
       <c r="O75" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="P75" t="s">
         <v>28</v>
       </c>
       <c r="Q75" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="R75" t="s">
         <v>27</v>
@@ -5370,13 +5400,13 @@
         <v>20</v>
       </c>
       <c r="D76" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E76" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F76" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G76" t="s">
         <v>25</v>
@@ -5388,28 +5418,28 @@
         <v>36</v>
       </c>
       <c r="J76" t="s">
+        <v>37</v>
+      </c>
+      <c r="K76" t="s">
+        <v>38</v>
+      </c>
+      <c r="L76" t="s">
+        <v>39</v>
+      </c>
+      <c r="M76" t="s">
+        <v>40</v>
+      </c>
+      <c r="N76" t="s">
+        <v>27</v>
+      </c>
+      <c r="O76" t="s">
         <v>45</v>
       </c>
-      <c r="K76" t="s">
-        <v>52</v>
-      </c>
-      <c r="L76" t="s">
-        <v>53</v>
-      </c>
-      <c r="M76" t="s">
-        <v>54</v>
-      </c>
-      <c r="N76" t="s">
-        <v>27</v>
-      </c>
-      <c r="O76" t="s">
-        <v>37</v>
-      </c>
       <c r="P76" t="s">
         <v>28</v>
       </c>
       <c r="Q76" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="R76" t="s">
         <v>27</v>
@@ -5429,34 +5459,34 @@
         <v>20</v>
       </c>
       <c r="D77" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E77" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F77" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G77" t="s">
         <v>25</v>
       </c>
       <c r="H77" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I77" t="s">
         <v>36</v>
       </c>
       <c r="J77" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K77" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L77" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="M77" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="N77" t="s">
         <v>27</v>
@@ -5468,7 +5498,7 @@
         <v>28</v>
       </c>
       <c r="Q77" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="R77" t="s">
         <v>27</v>
@@ -5488,46 +5518,46 @@
         <v>20</v>
       </c>
       <c r="D78" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E78" t="s">
         <v>51</v>
       </c>
       <c r="F78" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G78" t="s">
         <v>25</v>
       </c>
       <c r="H78" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I78" t="s">
         <v>36</v>
       </c>
       <c r="J78" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K78" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L78" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="M78" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="N78" t="s">
         <v>27</v>
       </c>
       <c r="O78" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="P78" t="s">
         <v>28</v>
       </c>
       <c r="Q78" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="R78" t="s">
         <v>27</v>
@@ -5547,46 +5577,46 @@
         <v>20</v>
       </c>
       <c r="D79" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E79" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F79" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G79" t="s">
         <v>25</v>
       </c>
       <c r="H79" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I79" t="s">
         <v>36</v>
       </c>
       <c r="J79" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K79" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="L79" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="M79" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="N79" t="s">
         <v>27</v>
       </c>
       <c r="O79" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="P79" t="s">
         <v>28</v>
       </c>
       <c r="Q79" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="R79" t="s">
         <v>27</v>
@@ -5606,19 +5636,19 @@
         <v>20</v>
       </c>
       <c r="D80" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E80" t="s">
         <v>23</v>
       </c>
       <c r="F80" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G80" t="s">
         <v>25</v>
       </c>
       <c r="H80" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I80" t="s">
         <v>36</v>
@@ -5627,25 +5657,25 @@
         <v>45</v>
       </c>
       <c r="K80" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="L80" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="M80" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="N80" t="s">
         <v>27</v>
       </c>
       <c r="O80" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="P80" t="s">
         <v>28</v>
       </c>
       <c r="Q80" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="R80" t="s">
         <v>27</v>
@@ -5665,19 +5695,19 @@
         <v>20</v>
       </c>
       <c r="D81" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E81" t="s">
         <v>23</v>
       </c>
       <c r="F81" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G81" t="s">
         <v>25</v>
       </c>
       <c r="H81" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I81" t="s">
         <v>36</v>
@@ -5698,13 +5728,13 @@
         <v>27</v>
       </c>
       <c r="O81" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="P81" t="s">
         <v>28</v>
       </c>
       <c r="Q81" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="R81" t="s">
         <v>27</v>
@@ -5721,52 +5751,52 @@
         <v>21</v>
       </c>
       <c r="C82" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="D82" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="E82" t="s">
         <v>23</v>
       </c>
       <c r="F82" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="G82" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H82" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I82" t="s">
         <v>36</v>
       </c>
       <c r="J82" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="K82" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="L82" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="M82" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N82" t="s">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="O82" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="P82" t="s">
         <v>28</v>
       </c>
       <c r="Q82" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="R82" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="S82" t="s">
         <v>146</v>
@@ -5774,28 +5804,28 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B83" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C83" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="D83" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="E83" t="s">
         <v>23</v>
       </c>
       <c r="F83" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="G83" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H83" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I83" t="s">
         <v>36</v>
@@ -5813,263 +5843,263 @@
         <v>43</v>
       </c>
       <c r="N83" t="s">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="O83" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="P83" t="s">
         <v>28</v>
       </c>
       <c r="Q83" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="R83" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="S83" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B84" t="s">
         <v>21</v>
       </c>
       <c r="C84" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="D84" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="E84" t="s">
         <v>23</v>
       </c>
       <c r="F84" t="s">
+        <v>137</v>
+      </c>
+      <c r="G84" t="s">
+        <v>25</v>
+      </c>
+      <c r="H84" t="s">
+        <v>26</v>
+      </c>
+      <c r="I84" t="s">
+        <v>36</v>
+      </c>
+      <c r="J84" t="s">
+        <v>37</v>
+      </c>
+      <c r="K84" t="s">
+        <v>38</v>
+      </c>
+      <c r="L84" t="s">
+        <v>42</v>
+      </c>
+      <c r="M84" t="s">
+        <v>43</v>
+      </c>
+      <c r="N84" t="s">
+        <v>27</v>
+      </c>
+      <c r="O84" t="s">
+        <v>37</v>
+      </c>
+      <c r="P84" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>138</v>
+      </c>
+      <c r="R84" t="s">
+        <v>27</v>
+      </c>
+      <c r="S84" t="s">
         <v>148</v>
-      </c>
-      <c r="G84" t="s">
-        <v>35</v>
-      </c>
-      <c r="H84" t="s">
-        <v>27</v>
-      </c>
-      <c r="I84" t="s">
-        <v>36</v>
-      </c>
-      <c r="J84" t="s">
-        <v>45</v>
-      </c>
-      <c r="K84" t="s">
-        <v>46</v>
-      </c>
-      <c r="L84" t="s">
-        <v>47</v>
-      </c>
-      <c r="M84" t="s">
-        <v>48</v>
-      </c>
-      <c r="N84" t="s">
-        <v>149</v>
-      </c>
-      <c r="O84" t="s">
-        <v>27</v>
-      </c>
-      <c r="P84" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q84" t="s">
-        <v>27</v>
-      </c>
-      <c r="R84" t="s">
-        <v>78</v>
-      </c>
-      <c r="S84" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B85" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C85" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="D85" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="E85" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F85" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="G85" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H85" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I85" t="s">
         <v>36</v>
       </c>
       <c r="J85" t="s">
+        <v>37</v>
+      </c>
+      <c r="K85" t="s">
+        <v>38</v>
+      </c>
+      <c r="L85" t="s">
+        <v>42</v>
+      </c>
+      <c r="M85" t="s">
+        <v>43</v>
+      </c>
+      <c r="N85" t="s">
+        <v>27</v>
+      </c>
+      <c r="O85" t="s">
         <v>45</v>
       </c>
-      <c r="K85" t="s">
-        <v>46</v>
-      </c>
-      <c r="L85" t="s">
-        <v>47</v>
-      </c>
-      <c r="M85" t="s">
-        <v>48</v>
-      </c>
-      <c r="N85" t="s">
+      <c r="P85" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>138</v>
+      </c>
+      <c r="R85" t="s">
+        <v>27</v>
+      </c>
+      <c r="S85" t="s">
         <v>149</v>
-      </c>
-      <c r="O85" t="s">
-        <v>27</v>
-      </c>
-      <c r="P85" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q85" t="s">
-        <v>27</v>
-      </c>
-      <c r="R85" t="s">
-        <v>78</v>
-      </c>
-      <c r="S85" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B86" t="s">
         <v>21</v>
       </c>
       <c r="C86" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="D86" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="E86" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F86" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="G86" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H86" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I86" t="s">
         <v>36</v>
       </c>
       <c r="J86" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="K86" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="L86" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="M86" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="N86" t="s">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="O86" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="P86" t="s">
         <v>28</v>
       </c>
       <c r="Q86" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="R86" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="S86" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B87" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C87" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="D87" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="E87" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F87" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="G87" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H87" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I87" t="s">
         <v>36</v>
       </c>
       <c r="J87" t="s">
+        <v>37</v>
+      </c>
+      <c r="K87" t="s">
+        <v>38</v>
+      </c>
+      <c r="L87" t="s">
+        <v>39</v>
+      </c>
+      <c r="M87" t="s">
+        <v>40</v>
+      </c>
+      <c r="N87" t="s">
+        <v>27</v>
+      </c>
+      <c r="O87" t="s">
         <v>45</v>
       </c>
-      <c r="K87" t="s">
-        <v>52</v>
-      </c>
-      <c r="L87" t="s">
-        <v>53</v>
-      </c>
-      <c r="M87" t="s">
-        <v>54</v>
-      </c>
-      <c r="N87" t="s">
-        <v>149</v>
-      </c>
-      <c r="O87" t="s">
-        <v>27</v>
-      </c>
       <c r="P87" t="s">
         <v>28</v>
       </c>
       <c r="Q87" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="R87" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="S87" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B88" t="s">
         <v>21</v>
@@ -6078,34 +6108,34 @@
         <v>20</v>
       </c>
       <c r="D88" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="E88" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="F88" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="G88" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H88" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I88" t="s">
         <v>36</v>
       </c>
       <c r="J88" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="K88" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="L88" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="M88" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="N88" t="s">
         <v>27</v>
@@ -6117,18 +6147,18 @@
         <v>28</v>
       </c>
       <c r="Q88" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="R88" t="s">
         <v>27</v>
       </c>
       <c r="S88" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B89" t="s">
         <v>21</v>
@@ -6137,34 +6167,34 @@
         <v>20</v>
       </c>
       <c r="D89" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="E89" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="F89" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="G89" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H89" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I89" t="s">
         <v>36</v>
       </c>
       <c r="J89" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="K89" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="L89" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="M89" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="N89" t="s">
         <v>27</v>
@@ -6176,18 +6206,18 @@
         <v>28</v>
       </c>
       <c r="Q89" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="R89" t="s">
         <v>27</v>
       </c>
       <c r="S89" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B90" t="s">
         <v>21</v>
@@ -6196,34 +6226,34 @@
         <v>20</v>
       </c>
       <c r="D90" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="E90" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="F90" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="G90" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H90" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I90" t="s">
         <v>36</v>
       </c>
       <c r="J90" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="K90" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="L90" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="M90" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="N90" t="s">
         <v>27</v>
@@ -6235,18 +6265,18 @@
         <v>28</v>
       </c>
       <c r="Q90" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="R90" t="s">
         <v>27</v>
       </c>
       <c r="S90" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B91" t="s">
         <v>21</v>
@@ -6255,78 +6285,78 @@
         <v>20</v>
       </c>
       <c r="D91" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="E91" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F91" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="G91" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H91" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I91" t="s">
         <v>36</v>
       </c>
       <c r="J91" t="s">
+        <v>45</v>
+      </c>
+      <c r="K91" t="s">
+        <v>52</v>
+      </c>
+      <c r="L91" t="s">
+        <v>53</v>
+      </c>
+      <c r="M91" t="s">
+        <v>54</v>
+      </c>
+      <c r="N91" t="s">
+        <v>27</v>
+      </c>
+      <c r="O91" t="s">
         <v>37</v>
       </c>
-      <c r="K91" t="s">
-        <v>38</v>
-      </c>
-      <c r="L91" t="s">
-        <v>42</v>
-      </c>
-      <c r="M91" t="s">
-        <v>43</v>
-      </c>
-      <c r="N91" t="s">
-        <v>27</v>
-      </c>
-      <c r="O91" t="s">
-        <v>58</v>
-      </c>
       <c r="P91" t="s">
         <v>28</v>
       </c>
       <c r="Q91" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="R91" t="s">
         <v>27</v>
       </c>
       <c r="S91" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B92" t="s">
         <v>21</v>
       </c>
       <c r="C92" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="D92" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E92" t="s">
         <v>23</v>
       </c>
       <c r="F92" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G92" t="s">
         <v>35</v>
       </c>
       <c r="H92" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I92" t="s">
         <v>36</v>
@@ -6344,48 +6374,48 @@
         <v>43</v>
       </c>
       <c r="N92" t="s">
-        <v>27</v>
+        <v>159</v>
       </c>
       <c r="O92" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="P92" t="s">
         <v>28</v>
       </c>
       <c r="Q92" t="s">
-        <v>157</v>
+        <v>27</v>
       </c>
       <c r="R92" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="S92" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B93" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C93" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="D93" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E93" t="s">
         <v>23</v>
       </c>
       <c r="F93" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G93" t="s">
         <v>35</v>
       </c>
       <c r="H93" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I93" t="s">
         <v>36</v>
@@ -6403,225 +6433,225 @@
         <v>43</v>
       </c>
       <c r="N93" t="s">
-        <v>27</v>
+        <v>159</v>
       </c>
       <c r="O93" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="P93" t="s">
         <v>28</v>
       </c>
       <c r="Q93" t="s">
-        <v>157</v>
+        <v>27</v>
       </c>
       <c r="R93" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="S93" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B94" t="s">
         <v>21</v>
       </c>
       <c r="C94" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="D94" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E94" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F94" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G94" t="s">
         <v>35</v>
       </c>
       <c r="H94" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I94" t="s">
         <v>36</v>
       </c>
       <c r="J94" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K94" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L94" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="M94" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="N94" t="s">
-        <v>27</v>
+        <v>159</v>
       </c>
       <c r="O94" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="P94" t="s">
         <v>28</v>
       </c>
       <c r="Q94" t="s">
-        <v>157</v>
+        <v>27</v>
       </c>
       <c r="R94" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="S94" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B95" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C95" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="D95" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E95" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="F95" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G95" t="s">
         <v>35</v>
       </c>
       <c r="H95" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I95" t="s">
         <v>36</v>
       </c>
       <c r="J95" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K95" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L95" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="M95" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="N95" t="s">
-        <v>27</v>
+        <v>159</v>
       </c>
       <c r="O95" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="P95" t="s">
         <v>28</v>
       </c>
       <c r="Q95" t="s">
-        <v>157</v>
+        <v>27</v>
       </c>
       <c r="R95" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="S95" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B96" t="s">
         <v>21</v>
       </c>
       <c r="C96" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="D96" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E96" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F96" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G96" t="s">
         <v>35</v>
       </c>
       <c r="H96" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I96" t="s">
         <v>36</v>
       </c>
       <c r="J96" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K96" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="L96" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="M96" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="N96" t="s">
-        <v>27</v>
+        <v>159</v>
       </c>
       <c r="O96" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="P96" t="s">
         <v>28</v>
       </c>
       <c r="Q96" t="s">
-        <v>157</v>
+        <v>27</v>
       </c>
       <c r="R96" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="S96" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B97" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C97" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="D97" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E97" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F97" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G97" t="s">
         <v>35</v>
       </c>
       <c r="H97" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I97" t="s">
         <v>36</v>
@@ -6630,51 +6660,51 @@
         <v>45</v>
       </c>
       <c r="K97" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="L97" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="M97" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="N97" t="s">
-        <v>27</v>
+        <v>159</v>
       </c>
       <c r="O97" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="P97" t="s">
         <v>28</v>
       </c>
       <c r="Q97" t="s">
-        <v>157</v>
+        <v>27</v>
       </c>
       <c r="R97" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="S97" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
+        <v>165</v>
+      </c>
+      <c r="B98" t="s">
+        <v>21</v>
+      </c>
+      <c r="C98" t="s">
+        <v>20</v>
+      </c>
+      <c r="D98" t="s">
+        <v>166</v>
+      </c>
+      <c r="E98" t="s">
+        <v>68</v>
+      </c>
+      <c r="F98" t="s">
         <v>167</v>
-      </c>
-      <c r="B98" t="s">
-        <v>21</v>
-      </c>
-      <c r="C98" t="s">
-        <v>20</v>
-      </c>
-      <c r="D98" t="s">
-        <v>156</v>
-      </c>
-      <c r="E98" t="s">
-        <v>20</v>
-      </c>
-      <c r="F98" t="s">
-        <v>157</v>
       </c>
       <c r="G98" t="s">
         <v>35</v>
@@ -6686,34 +6716,34 @@
         <v>36</v>
       </c>
       <c r="J98" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="K98" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="L98" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="M98" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="N98" t="s">
         <v>27</v>
       </c>
       <c r="O98" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="P98" t="s">
         <v>28</v>
       </c>
       <c r="Q98" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="R98" t="s">
         <v>27</v>
       </c>
       <c r="S98" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="99">
@@ -6727,13 +6757,13 @@
         <v>20</v>
       </c>
       <c r="D99" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E99" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F99" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="G99" t="s">
         <v>35</v>
@@ -6745,28 +6775,28 @@
         <v>36</v>
       </c>
       <c r="J99" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="K99" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="L99" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="M99" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="N99" t="s">
         <v>27</v>
       </c>
       <c r="O99" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="P99" t="s">
         <v>28</v>
       </c>
       <c r="Q99" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="R99" t="s">
         <v>27</v>
@@ -6786,13 +6816,13 @@
         <v>20</v>
       </c>
       <c r="D100" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E100" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="F100" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="G100" t="s">
         <v>35</v>
@@ -6804,28 +6834,28 @@
         <v>36</v>
       </c>
       <c r="J100" t="s">
+        <v>58</v>
+      </c>
+      <c r="K100" t="s">
+        <v>59</v>
+      </c>
+      <c r="L100" t="s">
+        <v>60</v>
+      </c>
+      <c r="M100" t="s">
+        <v>61</v>
+      </c>
+      <c r="N100" t="s">
+        <v>27</v>
+      </c>
+      <c r="O100" t="s">
         <v>45</v>
       </c>
-      <c r="K100" t="s">
-        <v>52</v>
-      </c>
-      <c r="L100" t="s">
-        <v>53</v>
-      </c>
-      <c r="M100" t="s">
-        <v>54</v>
-      </c>
-      <c r="N100" t="s">
-        <v>27</v>
-      </c>
-      <c r="O100" t="s">
-        <v>58</v>
-      </c>
       <c r="P100" t="s">
         <v>28</v>
       </c>
       <c r="Q100" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="R100" t="s">
         <v>27</v>
@@ -6845,13 +6875,13 @@
         <v>20</v>
       </c>
       <c r="D101" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E101" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F101" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="G101" t="s">
         <v>35</v>
@@ -6863,28 +6893,28 @@
         <v>36</v>
       </c>
       <c r="J101" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="K101" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="L101" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M101" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="N101" t="s">
         <v>27</v>
       </c>
       <c r="O101" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="P101" t="s">
         <v>28</v>
       </c>
       <c r="Q101" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="R101" t="s">
         <v>27</v>
@@ -6904,13 +6934,13 @@
         <v>20</v>
       </c>
       <c r="D102" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E102" t="s">
         <v>23</v>
       </c>
       <c r="F102" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="G102" t="s">
         <v>35</v>
@@ -6922,28 +6952,28 @@
         <v>36</v>
       </c>
       <c r="J102" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="K102" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="L102" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M102" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="N102" t="s">
         <v>27</v>
       </c>
       <c r="O102" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="P102" t="s">
         <v>28</v>
       </c>
       <c r="Q102" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="R102" t="s">
         <v>27</v>
@@ -6963,46 +6993,46 @@
         <v>20</v>
       </c>
       <c r="D103" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E103" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F103" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="G103" t="s">
         <v>35</v>
       </c>
       <c r="H103" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I103" t="s">
         <v>36</v>
       </c>
       <c r="J103" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="K103" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="L103" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="M103" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="N103" t="s">
         <v>27</v>
       </c>
       <c r="O103" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="P103" t="s">
         <v>28</v>
       </c>
       <c r="Q103" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="R103" t="s">
         <v>27</v>
@@ -7022,46 +7052,46 @@
         <v>20</v>
       </c>
       <c r="D104" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E104" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F104" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="G104" t="s">
         <v>35</v>
       </c>
       <c r="H104" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I104" t="s">
         <v>36</v>
       </c>
       <c r="J104" t="s">
+        <v>37</v>
+      </c>
+      <c r="K104" t="s">
+        <v>38</v>
+      </c>
+      <c r="L104" t="s">
+        <v>39</v>
+      </c>
+      <c r="M104" t="s">
+        <v>40</v>
+      </c>
+      <c r="N104" t="s">
+        <v>27</v>
+      </c>
+      <c r="O104" t="s">
         <v>58</v>
       </c>
-      <c r="K104" t="s">
-        <v>59</v>
-      </c>
-      <c r="L104" t="s">
-        <v>60</v>
-      </c>
-      <c r="M104" t="s">
-        <v>61</v>
-      </c>
-      <c r="N104" t="s">
-        <v>27</v>
-      </c>
-      <c r="O104" t="s">
-        <v>45</v>
-      </c>
       <c r="P104" t="s">
         <v>28</v>
       </c>
       <c r="Q104" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="R104" t="s">
         <v>27</v>
@@ -7081,19 +7111,19 @@
         <v>20</v>
       </c>
       <c r="D105" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E105" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F105" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="G105" t="s">
         <v>35</v>
       </c>
       <c r="H105" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I105" t="s">
         <v>36</v>
@@ -7105,22 +7135,22 @@
         <v>38</v>
       </c>
       <c r="L105" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="M105" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N105" t="s">
         <v>27</v>
       </c>
       <c r="O105" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="P105" t="s">
         <v>28</v>
       </c>
       <c r="Q105" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="R105" t="s">
         <v>27</v>
@@ -7140,19 +7170,19 @@
         <v>20</v>
       </c>
       <c r="D106" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E106" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F106" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="G106" t="s">
         <v>35</v>
       </c>
       <c r="H106" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I106" t="s">
         <v>36</v>
@@ -7164,22 +7194,22 @@
         <v>38</v>
       </c>
       <c r="L106" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="M106" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N106" t="s">
         <v>27</v>
       </c>
       <c r="O106" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="P106" t="s">
         <v>28</v>
       </c>
       <c r="Q106" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="R106" t="s">
         <v>27</v>
@@ -7199,46 +7229,46 @@
         <v>20</v>
       </c>
       <c r="D107" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E107" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F107" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="G107" t="s">
         <v>35</v>
       </c>
       <c r="H107" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I107" t="s">
         <v>36</v>
       </c>
       <c r="J107" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K107" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L107" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="M107" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="N107" t="s">
         <v>27</v>
       </c>
       <c r="O107" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="P107" t="s">
         <v>28</v>
       </c>
       <c r="Q107" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="R107" t="s">
         <v>27</v>
@@ -7258,46 +7288,46 @@
         <v>20</v>
       </c>
       <c r="D108" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E108" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F108" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="G108" t="s">
         <v>35</v>
       </c>
       <c r="H108" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I108" t="s">
         <v>36</v>
       </c>
       <c r="J108" t="s">
+        <v>45</v>
+      </c>
+      <c r="K108" t="s">
+        <v>46</v>
+      </c>
+      <c r="L108" t="s">
+        <v>47</v>
+      </c>
+      <c r="M108" t="s">
+        <v>48</v>
+      </c>
+      <c r="N108" t="s">
+        <v>27</v>
+      </c>
+      <c r="O108" t="s">
         <v>37</v>
       </c>
-      <c r="K108" t="s">
-        <v>38</v>
-      </c>
-      <c r="L108" t="s">
-        <v>39</v>
-      </c>
-      <c r="M108" t="s">
-        <v>40</v>
-      </c>
-      <c r="N108" t="s">
-        <v>27</v>
-      </c>
-      <c r="O108" t="s">
-        <v>58</v>
-      </c>
       <c r="P108" t="s">
         <v>28</v>
       </c>
       <c r="Q108" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="R108" t="s">
         <v>27</v>
@@ -7317,46 +7347,46 @@
         <v>20</v>
       </c>
       <c r="D109" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E109" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="F109" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="G109" t="s">
         <v>35</v>
       </c>
       <c r="H109" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I109" t="s">
         <v>36</v>
       </c>
       <c r="J109" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K109" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L109" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="M109" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="N109" t="s">
         <v>27</v>
       </c>
       <c r="O109" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="P109" t="s">
         <v>28</v>
       </c>
       <c r="Q109" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="R109" t="s">
         <v>27</v>
@@ -7376,46 +7406,46 @@
         <v>20</v>
       </c>
       <c r="D110" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E110" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F110" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="G110" t="s">
         <v>35</v>
       </c>
       <c r="H110" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I110" t="s">
         <v>36</v>
       </c>
       <c r="J110" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K110" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="L110" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="M110" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="N110" t="s">
         <v>27</v>
       </c>
       <c r="O110" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="P110" t="s">
         <v>28</v>
       </c>
       <c r="Q110" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="R110" t="s">
         <v>27</v>
@@ -7435,19 +7465,19 @@
         <v>20</v>
       </c>
       <c r="D111" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E111" t="s">
         <v>23</v>
       </c>
       <c r="F111" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="G111" t="s">
         <v>35</v>
       </c>
       <c r="H111" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I111" t="s">
         <v>36</v>
@@ -7456,13 +7486,13 @@
         <v>45</v>
       </c>
       <c r="K111" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="L111" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="M111" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="N111" t="s">
         <v>27</v>
@@ -7474,7 +7504,7 @@
         <v>28</v>
       </c>
       <c r="Q111" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="R111" t="s">
         <v>27</v>
@@ -7494,19 +7524,19 @@
         <v>20</v>
       </c>
       <c r="D112" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E112" t="s">
         <v>23</v>
       </c>
       <c r="F112" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="G112" t="s">
         <v>35</v>
       </c>
       <c r="H112" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I112" t="s">
         <v>36</v>
@@ -7515,13 +7545,13 @@
         <v>45</v>
       </c>
       <c r="K112" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="L112" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="M112" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="N112" t="s">
         <v>27</v>
@@ -7533,7 +7563,7 @@
         <v>28</v>
       </c>
       <c r="Q112" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="R112" t="s">
         <v>27</v>
@@ -7553,13 +7583,13 @@
         <v>20</v>
       </c>
       <c r="D113" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E113" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F113" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="G113" t="s">
         <v>35</v>
@@ -7571,16 +7601,16 @@
         <v>36</v>
       </c>
       <c r="J113" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="K113" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="L113" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="M113" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="N113" t="s">
         <v>27</v>
@@ -7592,7 +7622,7 @@
         <v>28</v>
       </c>
       <c r="Q113" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="R113" t="s">
         <v>27</v>
@@ -7612,13 +7642,13 @@
         <v>20</v>
       </c>
       <c r="D114" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E114" t="s">
         <v>23</v>
       </c>
       <c r="F114" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="G114" t="s">
         <v>35</v>
@@ -7630,28 +7660,28 @@
         <v>36</v>
       </c>
       <c r="J114" t="s">
+        <v>58</v>
+      </c>
+      <c r="K114" t="s">
+        <v>59</v>
+      </c>
+      <c r="L114" t="s">
+        <v>60</v>
+      </c>
+      <c r="M114" t="s">
+        <v>61</v>
+      </c>
+      <c r="N114" t="s">
+        <v>27</v>
+      </c>
+      <c r="O114" t="s">
         <v>45</v>
       </c>
-      <c r="K114" t="s">
-        <v>52</v>
-      </c>
-      <c r="L114" t="s">
-        <v>53</v>
-      </c>
-      <c r="M114" t="s">
-        <v>54</v>
-      </c>
-      <c r="N114" t="s">
-        <v>27</v>
-      </c>
-      <c r="O114" t="s">
-        <v>37</v>
-      </c>
       <c r="P114" t="s">
         <v>28</v>
       </c>
       <c r="Q114" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="R114" t="s">
         <v>27</v>
@@ -7671,13 +7701,13 @@
         <v>20</v>
       </c>
       <c r="D115" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E115" t="s">
         <v>51</v>
       </c>
       <c r="F115" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="G115" t="s">
         <v>35</v>
@@ -7689,28 +7719,28 @@
         <v>36</v>
       </c>
       <c r="J115" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="K115" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="L115" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M115" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="N115" t="s">
         <v>27</v>
       </c>
       <c r="O115" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="P115" t="s">
         <v>28</v>
       </c>
       <c r="Q115" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="R115" t="s">
         <v>27</v>
@@ -7727,52 +7757,52 @@
         <v>21</v>
       </c>
       <c r="C116" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D116" t="s">
-        <v>22</v>
+        <v>166</v>
       </c>
       <c r="E116" t="s">
         <v>23</v>
       </c>
       <c r="F116" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="G116" t="s">
-        <v>187</v>
+        <v>35</v>
       </c>
       <c r="H116" t="s">
         <v>26</v>
       </c>
       <c r="I116" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="J116" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="K116" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="L116" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="M116" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="N116" t="s">
         <v>27</v>
       </c>
       <c r="O116" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="P116" t="s">
         <v>28</v>
       </c>
       <c r="Q116" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="R116" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="S116" t="s">
         <v>185</v>
@@ -7780,205 +7810,205 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B117" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C117" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D117" t="s">
-        <v>22</v>
+        <v>166</v>
       </c>
       <c r="E117" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F117" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="G117" t="s">
-        <v>187</v>
+        <v>35</v>
       </c>
       <c r="H117" t="s">
         <v>26</v>
       </c>
       <c r="I117" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="J117" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="K117" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="L117" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="M117" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="N117" t="s">
         <v>27</v>
       </c>
       <c r="O117" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="P117" t="s">
         <v>28</v>
       </c>
       <c r="Q117" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="R117" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="S117" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B118" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C118" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D118" t="s">
-        <v>22</v>
+        <v>166</v>
       </c>
       <c r="E118" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F118" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="G118" t="s">
+        <v>35</v>
+      </c>
+      <c r="H118" t="s">
+        <v>26</v>
+      </c>
+      <c r="I118" t="s">
+        <v>36</v>
+      </c>
+      <c r="J118" t="s">
+        <v>37</v>
+      </c>
+      <c r="K118" t="s">
+        <v>38</v>
+      </c>
+      <c r="L118" t="s">
+        <v>39</v>
+      </c>
+      <c r="M118" t="s">
+        <v>40</v>
+      </c>
+      <c r="N118" t="s">
+        <v>27</v>
+      </c>
+      <c r="O118" t="s">
+        <v>58</v>
+      </c>
+      <c r="P118" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>167</v>
+      </c>
+      <c r="R118" t="s">
+        <v>27</v>
+      </c>
+      <c r="S118" t="s">
         <v>187</v>
-      </c>
-      <c r="H118" t="s">
-        <v>30</v>
-      </c>
-      <c r="I118" t="s">
-        <v>27</v>
-      </c>
-      <c r="J118" t="s">
-        <v>27</v>
-      </c>
-      <c r="K118" t="s">
-        <v>27</v>
-      </c>
-      <c r="L118" t="s">
-        <v>27</v>
-      </c>
-      <c r="M118" t="s">
-        <v>27</v>
-      </c>
-      <c r="N118" t="s">
-        <v>27</v>
-      </c>
-      <c r="O118" t="s">
-        <v>27</v>
-      </c>
-      <c r="P118" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q118" t="s">
-        <v>27</v>
-      </c>
-      <c r="R118" t="s">
-        <v>24</v>
-      </c>
-      <c r="S118" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B119" t="s">
         <v>21</v>
       </c>
       <c r="C119" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D119" t="s">
-        <v>56</v>
+        <v>166</v>
       </c>
       <c r="E119" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="F119" t="s">
-        <v>57</v>
+        <v>167</v>
       </c>
       <c r="G119" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H119" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I119" t="s">
         <v>36</v>
       </c>
       <c r="J119" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="K119" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="L119" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="M119" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="N119" t="s">
         <v>27</v>
       </c>
       <c r="O119" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="P119" t="s">
         <v>28</v>
       </c>
       <c r="Q119" t="s">
-        <v>57</v>
+        <v>167</v>
       </c>
       <c r="R119" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="S119" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B120" t="s">
         <v>21</v>
       </c>
       <c r="C120" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D120" t="s">
-        <v>56</v>
+        <v>166</v>
       </c>
       <c r="E120" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="F120" t="s">
-        <v>57</v>
+        <v>167</v>
       </c>
       <c r="G120" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H120" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I120" t="s">
         <v>36</v>
@@ -7990,113 +8020,113 @@
         <v>38</v>
       </c>
       <c r="L120" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="M120" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N120" t="s">
         <v>27</v>
       </c>
       <c r="O120" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="P120" t="s">
         <v>28</v>
       </c>
       <c r="Q120" t="s">
-        <v>57</v>
+        <v>167</v>
       </c>
       <c r="R120" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="S120" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B121" t="s">
         <v>21</v>
       </c>
       <c r="C121" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D121" t="s">
-        <v>56</v>
+        <v>166</v>
       </c>
       <c r="E121" t="s">
         <v>23</v>
       </c>
       <c r="F121" t="s">
-        <v>57</v>
+        <v>167</v>
       </c>
       <c r="G121" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H121" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I121" t="s">
         <v>36</v>
       </c>
       <c r="J121" t="s">
+        <v>45</v>
+      </c>
+      <c r="K121" t="s">
+        <v>46</v>
+      </c>
+      <c r="L121" t="s">
+        <v>47</v>
+      </c>
+      <c r="M121" t="s">
+        <v>48</v>
+      </c>
+      <c r="N121" t="s">
+        <v>27</v>
+      </c>
+      <c r="O121" t="s">
         <v>37</v>
       </c>
-      <c r="K121" t="s">
-        <v>38</v>
-      </c>
-      <c r="L121" t="s">
-        <v>39</v>
-      </c>
-      <c r="M121" t="s">
-        <v>40</v>
-      </c>
-      <c r="N121" t="s">
-        <v>27</v>
-      </c>
-      <c r="O121" t="s">
-        <v>27</v>
-      </c>
       <c r="P121" t="s">
         <v>28</v>
       </c>
       <c r="Q121" t="s">
-        <v>57</v>
+        <v>167</v>
       </c>
       <c r="R121" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="S121" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B122" t="s">
         <v>21</v>
       </c>
       <c r="C122" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D122" t="s">
-        <v>56</v>
+        <v>166</v>
       </c>
       <c r="E122" t="s">
         <v>23</v>
       </c>
       <c r="F122" t="s">
-        <v>57</v>
+        <v>167</v>
       </c>
       <c r="G122" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H122" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I122" t="s">
         <v>36</v>
@@ -8117,45 +8147,45 @@
         <v>27</v>
       </c>
       <c r="O122" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="P122" t="s">
         <v>28</v>
       </c>
       <c r="Q122" t="s">
-        <v>57</v>
+        <v>167</v>
       </c>
       <c r="R122" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="S122" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B123" t="s">
         <v>21</v>
       </c>
       <c r="C123" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D123" t="s">
-        <v>56</v>
+        <v>166</v>
       </c>
       <c r="E123" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="F123" t="s">
-        <v>57</v>
+        <v>167</v>
       </c>
       <c r="G123" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H123" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I123" t="s">
         <v>36</v>
@@ -8176,42 +8206,42 @@
         <v>27</v>
       </c>
       <c r="O123" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="P123" t="s">
         <v>28</v>
       </c>
       <c r="Q123" t="s">
-        <v>57</v>
+        <v>167</v>
       </c>
       <c r="R123" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="S123" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B124" t="s">
         <v>21</v>
       </c>
       <c r="C124" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D124" t="s">
-        <v>56</v>
+        <v>166</v>
       </c>
       <c r="E124" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F124" t="s">
-        <v>57</v>
+        <v>167</v>
       </c>
       <c r="G124" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H124" t="s">
         <v>26</v>
@@ -8223,54 +8253,54 @@
         <v>45</v>
       </c>
       <c r="K124" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="L124" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="M124" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="N124" t="s">
         <v>27</v>
       </c>
       <c r="O124" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="P124" t="s">
         <v>28</v>
       </c>
       <c r="Q124" t="s">
-        <v>57</v>
+        <v>167</v>
       </c>
       <c r="R124" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="S124" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B125" t="s">
         <v>21</v>
       </c>
       <c r="C125" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D125" t="s">
-        <v>56</v>
+        <v>166</v>
       </c>
       <c r="E125" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="F125" t="s">
-        <v>57</v>
+        <v>167</v>
       </c>
       <c r="G125" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H125" t="s">
         <v>26</v>
@@ -8279,39 +8309,39 @@
         <v>36</v>
       </c>
       <c r="J125" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K125" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="L125" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="M125" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="N125" t="s">
         <v>27</v>
       </c>
       <c r="O125" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="P125" t="s">
         <v>28</v>
       </c>
       <c r="Q125" t="s">
-        <v>57</v>
+        <v>167</v>
       </c>
       <c r="R125" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="S125" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B126" t="s">
         <v>21</v>
@@ -8320,52 +8350,642 @@
         <v>21</v>
       </c>
       <c r="D126" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="E126" t="s">
         <v>23</v>
       </c>
       <c r="F126" t="s">
-        <v>57</v>
+        <v>196</v>
       </c>
       <c r="G126" t="s">
-        <v>25</v>
+        <v>197</v>
       </c>
       <c r="H126" t="s">
         <v>26</v>
       </c>
       <c r="I126" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="J126" t="s">
+        <v>27</v>
+      </c>
+      <c r="K126" t="s">
+        <v>27</v>
+      </c>
+      <c r="L126" t="s">
+        <v>27</v>
+      </c>
+      <c r="M126" t="s">
+        <v>27</v>
+      </c>
+      <c r="N126" t="s">
+        <v>27</v>
+      </c>
+      <c r="O126" t="s">
+        <v>27</v>
+      </c>
+      <c r="P126" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>27</v>
+      </c>
+      <c r="R126" t="s">
+        <v>24</v>
+      </c>
+      <c r="S126" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>198</v>
+      </c>
+      <c r="B127" t="s">
+        <v>20</v>
+      </c>
+      <c r="C127" t="s">
+        <v>21</v>
+      </c>
+      <c r="D127" t="s">
+        <v>22</v>
+      </c>
+      <c r="E127" t="s">
+        <v>23</v>
+      </c>
+      <c r="F127" t="s">
+        <v>196</v>
+      </c>
+      <c r="G127" t="s">
+        <v>197</v>
+      </c>
+      <c r="H127" t="s">
+        <v>26</v>
+      </c>
+      <c r="I127" t="s">
+        <v>27</v>
+      </c>
+      <c r="J127" t="s">
+        <v>27</v>
+      </c>
+      <c r="K127" t="s">
+        <v>27</v>
+      </c>
+      <c r="L127" t="s">
+        <v>27</v>
+      </c>
+      <c r="M127" t="s">
+        <v>27</v>
+      </c>
+      <c r="N127" t="s">
+        <v>27</v>
+      </c>
+      <c r="O127" t="s">
+        <v>27</v>
+      </c>
+      <c r="P127" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>27</v>
+      </c>
+      <c r="R127" t="s">
+        <v>24</v>
+      </c>
+      <c r="S127" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>199</v>
+      </c>
+      <c r="B128" t="s">
+        <v>20</v>
+      </c>
+      <c r="C128" t="s">
+        <v>21</v>
+      </c>
+      <c r="D128" t="s">
+        <v>22</v>
+      </c>
+      <c r="E128" t="s">
+        <v>23</v>
+      </c>
+      <c r="F128" t="s">
+        <v>196</v>
+      </c>
+      <c r="G128" t="s">
+        <v>197</v>
+      </c>
+      <c r="H128" t="s">
+        <v>30</v>
+      </c>
+      <c r="I128" t="s">
+        <v>27</v>
+      </c>
+      <c r="J128" t="s">
+        <v>27</v>
+      </c>
+      <c r="K128" t="s">
+        <v>27</v>
+      </c>
+      <c r="L128" t="s">
+        <v>27</v>
+      </c>
+      <c r="M128" t="s">
+        <v>27</v>
+      </c>
+      <c r="N128" t="s">
+        <v>27</v>
+      </c>
+      <c r="O128" t="s">
+        <v>27</v>
+      </c>
+      <c r="P128" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>27</v>
+      </c>
+      <c r="R128" t="s">
+        <v>24</v>
+      </c>
+      <c r="S128" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>200</v>
+      </c>
+      <c r="B129" t="s">
+        <v>21</v>
+      </c>
+      <c r="C129" t="s">
+        <v>21</v>
+      </c>
+      <c r="D129" t="s">
+        <v>56</v>
+      </c>
+      <c r="E129" t="s">
+        <v>68</v>
+      </c>
+      <c r="F129" t="s">
+        <v>57</v>
+      </c>
+      <c r="G129" t="s">
+        <v>25</v>
+      </c>
+      <c r="H129" t="s">
+        <v>30</v>
+      </c>
+      <c r="I129" t="s">
+        <v>36</v>
+      </c>
+      <c r="J129" t="s">
+        <v>58</v>
+      </c>
+      <c r="K129" t="s">
+        <v>59</v>
+      </c>
+      <c r="L129" t="s">
+        <v>60</v>
+      </c>
+      <c r="M129" t="s">
+        <v>61</v>
+      </c>
+      <c r="N129" t="s">
+        <v>27</v>
+      </c>
+      <c r="O129" t="s">
+        <v>27</v>
+      </c>
+      <c r="P129" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>57</v>
+      </c>
+      <c r="R129" t="s">
+        <v>57</v>
+      </c>
+      <c r="S129" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>201</v>
+      </c>
+      <c r="B130" t="s">
+        <v>21</v>
+      </c>
+      <c r="C130" t="s">
+        <v>21</v>
+      </c>
+      <c r="D130" t="s">
+        <v>56</v>
+      </c>
+      <c r="E130" t="s">
+        <v>68</v>
+      </c>
+      <c r="F130" t="s">
+        <v>57</v>
+      </c>
+      <c r="G130" t="s">
+        <v>25</v>
+      </c>
+      <c r="H130" t="s">
+        <v>30</v>
+      </c>
+      <c r="I130" t="s">
+        <v>36</v>
+      </c>
+      <c r="J130" t="s">
+        <v>37</v>
+      </c>
+      <c r="K130" t="s">
+        <v>38</v>
+      </c>
+      <c r="L130" t="s">
+        <v>42</v>
+      </c>
+      <c r="M130" t="s">
+        <v>43</v>
+      </c>
+      <c r="N130" t="s">
+        <v>27</v>
+      </c>
+      <c r="O130" t="s">
+        <v>27</v>
+      </c>
+      <c r="P130" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>57</v>
+      </c>
+      <c r="R130" t="s">
+        <v>57</v>
+      </c>
+      <c r="S130" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>202</v>
+      </c>
+      <c r="B131" t="s">
+        <v>21</v>
+      </c>
+      <c r="C131" t="s">
+        <v>21</v>
+      </c>
+      <c r="D131" t="s">
+        <v>56</v>
+      </c>
+      <c r="E131" t="s">
+        <v>23</v>
+      </c>
+      <c r="F131" t="s">
+        <v>57</v>
+      </c>
+      <c r="G131" t="s">
+        <v>25</v>
+      </c>
+      <c r="H131" t="s">
+        <v>30</v>
+      </c>
+      <c r="I131" t="s">
+        <v>36</v>
+      </c>
+      <c r="J131" t="s">
+        <v>37</v>
+      </c>
+      <c r="K131" t="s">
+        <v>38</v>
+      </c>
+      <c r="L131" t="s">
+        <v>39</v>
+      </c>
+      <c r="M131" t="s">
+        <v>40</v>
+      </c>
+      <c r="N131" t="s">
+        <v>27</v>
+      </c>
+      <c r="O131" t="s">
+        <v>27</v>
+      </c>
+      <c r="P131" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q131" t="s">
+        <v>57</v>
+      </c>
+      <c r="R131" t="s">
+        <v>57</v>
+      </c>
+      <c r="S131" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>203</v>
+      </c>
+      <c r="B132" t="s">
+        <v>21</v>
+      </c>
+      <c r="C132" t="s">
+        <v>21</v>
+      </c>
+      <c r="D132" t="s">
+        <v>56</v>
+      </c>
+      <c r="E132" t="s">
+        <v>23</v>
+      </c>
+      <c r="F132" t="s">
+        <v>57</v>
+      </c>
+      <c r="G132" t="s">
+        <v>25</v>
+      </c>
+      <c r="H132" t="s">
+        <v>30</v>
+      </c>
+      <c r="I132" t="s">
+        <v>36</v>
+      </c>
+      <c r="J132" t="s">
         <v>45</v>
       </c>
-      <c r="K126" t="s">
+      <c r="K132" t="s">
+        <v>46</v>
+      </c>
+      <c r="L132" t="s">
+        <v>47</v>
+      </c>
+      <c r="M132" t="s">
+        <v>48</v>
+      </c>
+      <c r="N132" t="s">
+        <v>27</v>
+      </c>
+      <c r="O132" t="s">
+        <v>27</v>
+      </c>
+      <c r="P132" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q132" t="s">
+        <v>57</v>
+      </c>
+      <c r="R132" t="s">
+        <v>57</v>
+      </c>
+      <c r="S132" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>204</v>
+      </c>
+      <c r="B133" t="s">
+        <v>21</v>
+      </c>
+      <c r="C133" t="s">
+        <v>21</v>
+      </c>
+      <c r="D133" t="s">
+        <v>56</v>
+      </c>
+      <c r="E133" t="s">
+        <v>68</v>
+      </c>
+      <c r="F133" t="s">
+        <v>57</v>
+      </c>
+      <c r="G133" t="s">
+        <v>25</v>
+      </c>
+      <c r="H133" t="s">
+        <v>30</v>
+      </c>
+      <c r="I133" t="s">
+        <v>36</v>
+      </c>
+      <c r="J133" t="s">
+        <v>45</v>
+      </c>
+      <c r="K133" t="s">
         <v>52</v>
       </c>
-      <c r="L126" t="s">
+      <c r="L133" t="s">
         <v>53</v>
       </c>
-      <c r="M126" t="s">
+      <c r="M133" t="s">
         <v>54</v>
       </c>
-      <c r="N126" t="s">
-        <v>27</v>
-      </c>
-      <c r="O126" t="s">
-        <v>27</v>
-      </c>
-      <c r="P126" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q126" t="s">
+      <c r="N133" t="s">
+        <v>27</v>
+      </c>
+      <c r="O133" t="s">
+        <v>27</v>
+      </c>
+      <c r="P133" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q133" t="s">
         <v>57</v>
       </c>
-      <c r="R126" t="s">
+      <c r="R133" t="s">
         <v>57</v>
       </c>
-      <c r="S126" t="s">
-        <v>197</v>
+      <c r="S133" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>205</v>
+      </c>
+      <c r="B134" t="s">
+        <v>21</v>
+      </c>
+      <c r="C134" t="s">
+        <v>21</v>
+      </c>
+      <c r="D134" t="s">
+        <v>56</v>
+      </c>
+      <c r="E134" t="s">
+        <v>20</v>
+      </c>
+      <c r="F134" t="s">
+        <v>57</v>
+      </c>
+      <c r="G134" t="s">
+        <v>25</v>
+      </c>
+      <c r="H134" t="s">
+        <v>26</v>
+      </c>
+      <c r="I134" t="s">
+        <v>36</v>
+      </c>
+      <c r="J134" t="s">
+        <v>45</v>
+      </c>
+      <c r="K134" t="s">
+        <v>46</v>
+      </c>
+      <c r="L134" t="s">
+        <v>47</v>
+      </c>
+      <c r="M134" t="s">
+        <v>48</v>
+      </c>
+      <c r="N134" t="s">
+        <v>27</v>
+      </c>
+      <c r="O134" t="s">
+        <v>27</v>
+      </c>
+      <c r="P134" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q134" t="s">
+        <v>57</v>
+      </c>
+      <c r="R134" t="s">
+        <v>57</v>
+      </c>
+      <c r="S134" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>206</v>
+      </c>
+      <c r="B135" t="s">
+        <v>21</v>
+      </c>
+      <c r="C135" t="s">
+        <v>21</v>
+      </c>
+      <c r="D135" t="s">
+        <v>56</v>
+      </c>
+      <c r="E135" t="s">
+        <v>68</v>
+      </c>
+      <c r="F135" t="s">
+        <v>57</v>
+      </c>
+      <c r="G135" t="s">
+        <v>25</v>
+      </c>
+      <c r="H135" t="s">
+        <v>26</v>
+      </c>
+      <c r="I135" t="s">
+        <v>36</v>
+      </c>
+      <c r="J135" t="s">
+        <v>37</v>
+      </c>
+      <c r="K135" t="s">
+        <v>38</v>
+      </c>
+      <c r="L135" t="s">
+        <v>39</v>
+      </c>
+      <c r="M135" t="s">
+        <v>40</v>
+      </c>
+      <c r="N135" t="s">
+        <v>27</v>
+      </c>
+      <c r="O135" t="s">
+        <v>27</v>
+      </c>
+      <c r="P135" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>57</v>
+      </c>
+      <c r="R135" t="s">
+        <v>57</v>
+      </c>
+      <c r="S135" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>207</v>
+      </c>
+      <c r="B136" t="s">
+        <v>21</v>
+      </c>
+      <c r="C136" t="s">
+        <v>21</v>
+      </c>
+      <c r="D136" t="s">
+        <v>56</v>
+      </c>
+      <c r="E136" t="s">
+        <v>23</v>
+      </c>
+      <c r="F136" t="s">
+        <v>57</v>
+      </c>
+      <c r="G136" t="s">
+        <v>25</v>
+      </c>
+      <c r="H136" t="s">
+        <v>26</v>
+      </c>
+      <c r="I136" t="s">
+        <v>36</v>
+      </c>
+      <c r="J136" t="s">
+        <v>45</v>
+      </c>
+      <c r="K136" t="s">
+        <v>52</v>
+      </c>
+      <c r="L136" t="s">
+        <v>53</v>
+      </c>
+      <c r="M136" t="s">
+        <v>54</v>
+      </c>
+      <c r="N136" t="s">
+        <v>27</v>
+      </c>
+      <c r="O136" t="s">
+        <v>27</v>
+      </c>
+      <c r="P136" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>57</v>
+      </c>
+      <c r="R136" t="s">
+        <v>57</v>
+      </c>
+      <c r="S136" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>
